--- a/pipeline_mapper/outputs/reporte_tda_final.xlsx
+++ b/pipeline_mapper/outputs/reporte_tda_final.xlsx
@@ -18,6 +18,7 @@
     <sheet name="ml_clasificacion" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="mapper_grid_search" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="mapper_gs_config" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="feature_importance" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19376,6 +19377,538 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>H_stat</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>p_value</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>p_fdr</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>eta_squared</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>kw_significativa</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>rf_imp_reg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>rf_imp_clf</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>rf_imp_mean</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>perm_imp_reg</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>perm_imp_reg_std</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>perm_imp_clf</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>perm_imp_clf_std</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>perm_imp_mean</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>composite_rank</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Edad madre</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>46.7699</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0316</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1563</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.1461</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1512</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0353</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.1988</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.0319</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.2209</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PN hijo (g)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.1619</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.922225</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.922225</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.2324</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.2012</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2168</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.1814</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.1558</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0238</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.1686</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Dif IMC</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.2489</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.882985</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.922225</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.2093</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.1947</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.202</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.1815</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0234</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.1404</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0222</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="O4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>EG hijo (sem)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>6.4713</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.039335</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.118005</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.1089</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.1039</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.1064</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.1084</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0204</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.08749999999999999</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0136</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Dif peso mamá</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.1831</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.912519</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.922225</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1016</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.1294</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.1155</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.07530000000000001</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.08309999999999999</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.07920000000000001</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5.33</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>12.4146</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.002015</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.009068</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-0.0382</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.009299999999999999</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-0.0372</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0.0377</v>
+      </c>
+      <c r="O7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>N° embarazo</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.6146</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.270547</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.608731</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.0478</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.0551</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.0514</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.0253</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.07389999999999999</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="O8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Región</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.5288</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.767649</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.922225</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0794</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.08890000000000001</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.08409999999999999</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0162</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-0.0289</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.0063</v>
+      </c>
+      <c r="O9" t="n">
+        <v>6.67</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sexo hijo</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.611</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.446872</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.80437</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.0143</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.0246</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.0195</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-0.0179</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.0282</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.0231</v>
+      </c>
+      <c r="O10" t="n">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
